--- a/server/excel/release/活动预告.xlsx
+++ b/server/excel/release/活动预告.xlsx
@@ -103,7 +103,7 @@
     <t xml:space="preserve">crossServeRankYBMan</t>
   </si>
   <si>
-    <t xml:space="preserve">Tiêu hao Nguyên bảo xếp hạng, Nguyên bảo tiêu hao càng nhiều kết toán thưởng càng tốt!</t>
+    <t xml:space="preserve">Tiêu hao Kim cương xếp hạng, Kim cương tiêu hao càng nhiều kết toán thưởng càng tốt!</t>
   </si>
   <si>
     <t xml:space="preserve">元宝排行</t>
@@ -151,7 +151,7 @@
     <t xml:space="preserve">仙器置换</t>
   </si>
   <si>
-    <t xml:space="preserve">Hoạt động trong lúc đó bên trong tiêu hao Nguyên bảo càng nhiều, có thể đạt được thưởng càng tốt!</t>
+    <t xml:space="preserve">Hoạt động trong lúc đó bên trong tiêu hao Kim cương càng nhiều, có thể đạt được thưởng càng tốt!</t>
   </si>
   <si>
     <t xml:space="preserve">xianqi</t>
